--- a/data/nzd0487/nzd0487.xlsx
+++ b/data/nzd0487/nzd0487.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E498"/>
+  <dimension ref="A1:E501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10890,6 +10890,69 @@
         <v>327.31</v>
       </c>
       <c r="E498" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:32+00:00</t>
+        </is>
+      </c>
+      <c r="B499" t="n">
+        <v>319.28</v>
+      </c>
+      <c r="C499" t="n">
+        <v>328.47</v>
+      </c>
+      <c r="D499" t="n">
+        <v>326.6</v>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B500" t="n">
+        <v>318.59</v>
+      </c>
+      <c r="C500" t="n">
+        <v>327.91</v>
+      </c>
+      <c r="D500" t="n">
+        <v>325.98</v>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:14:16+00:00</t>
+        </is>
+      </c>
+      <c r="B501" t="n">
+        <v>318.08</v>
+      </c>
+      <c r="C501" t="n">
+        <v>327.4</v>
+      </c>
+      <c r="D501" t="n">
+        <v>326.13</v>
+      </c>
+      <c r="E501" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -10906,7 +10969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B663"/>
+  <dimension ref="A1:B666"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17539,6 +17602,36 @@
       </c>
       <c r="B663" t="n">
         <v>-0.71</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B664" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B665" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B666" t="n">
+        <v>0.27</v>
       </c>
     </row>
   </sheetData>
@@ -17707,28 +17800,28 @@
         <v>0.07530000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.05893513480898363</v>
+        <v>-0.06693210436385585</v>
       </c>
       <c r="J2" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K2" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005779787422544702</v>
+        <v>0.007473128315773736</v>
       </c>
       <c r="M2" t="n">
-        <v>4.433872653200424</v>
+        <v>4.451824610556151</v>
       </c>
       <c r="N2" t="n">
-        <v>29.55435217174977</v>
+        <v>29.62801077299617</v>
       </c>
       <c r="O2" t="n">
-        <v>5.436391466013992</v>
+        <v>5.443161836010039</v>
       </c>
       <c r="P2" t="n">
-        <v>326.7446718768045</v>
+        <v>326.8389543044394</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17785,28 +17878,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07522243221598109</v>
+        <v>-0.0794280017263839</v>
       </c>
       <c r="J3" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K3" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02464057527438757</v>
+        <v>0.02756435604592211</v>
       </c>
       <c r="M3" t="n">
-        <v>2.629310874338245</v>
+        <v>2.631414591599939</v>
       </c>
       <c r="N3" t="n">
-        <v>11.07925974496869</v>
+        <v>11.08291472673469</v>
       </c>
       <c r="O3" t="n">
-        <v>3.328552199525897</v>
+        <v>3.329101189020046</v>
       </c>
       <c r="P3" t="n">
-        <v>333.3696824703266</v>
+        <v>333.4192679414205</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17863,28 +17956,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.07921508904918521</v>
+        <v>-0.09077081616439481</v>
       </c>
       <c r="J4" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K4" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02176469427849514</v>
+        <v>0.02772330224868846</v>
       </c>
       <c r="M4" t="n">
-        <v>2.897814944631342</v>
+        <v>2.93663139603497</v>
       </c>
       <c r="N4" t="n">
-        <v>13.95110959400751</v>
+        <v>14.38901610469076</v>
       </c>
       <c r="O4" t="n">
-        <v>3.735118417668644</v>
+        <v>3.793285660834254</v>
       </c>
       <c r="P4" t="n">
-        <v>337.7711335571437</v>
+        <v>337.9073651631218</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17922,7 +18015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E498"/>
+  <dimension ref="A1:E501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31371,6 +31464,87 @@
         </is>
       </c>
     </row>
+    <row r="499">
+      <c r="A499" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:32+00:00</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>-45.372205897167674,170.8660273170246</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>-45.372603221515995,170.86529652275803</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>-45.37307697752621,170.86467293017586</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>-45.37220048035955,170.86602301197544</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>-45.37259928142355,170.86529206602847</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>-45.37307323148016,170.8646670646373</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:14:16+00:00</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>-45.37219647663171,170.86601982998312</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>-45.372595693124936,170.86528800722178</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>-45.37307413778165,170.86466848371916</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0487/nzd0487.xlsx
+++ b/data/nzd0487/nzd0487.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E501"/>
+  <dimension ref="A1:E503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10953,6 +10953,48 @@
         <v>326.13</v>
       </c>
       <c r="E501" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B502" t="n">
+        <v>318.06</v>
+      </c>
+      <c r="C502" t="n">
+        <v>327.17</v>
+      </c>
+      <c r="D502" t="n">
+        <v>325.79</v>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:00+00:00</t>
+        </is>
+      </c>
+      <c r="B503" t="n">
+        <v>318.35</v>
+      </c>
+      <c r="C503" t="n">
+        <v>327.05</v>
+      </c>
+      <c r="D503" t="n">
+        <v>326</v>
+      </c>
+      <c r="E503" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -10969,7 +11011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B666"/>
+  <dimension ref="A1:B668"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17632,6 +17674,26 @@
       </c>
       <c r="B666" t="n">
         <v>0.27</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B667" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B668" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -17800,28 +17862,28 @@
         <v>0.07530000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.06693210436385585</v>
+        <v>-0.0725038898119062</v>
       </c>
       <c r="J2" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="K2" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007473128315773736</v>
+        <v>0.008777207173976564</v>
       </c>
       <c r="M2" t="n">
-        <v>4.451824610556151</v>
+        <v>4.465031315489406</v>
       </c>
       <c r="N2" t="n">
-        <v>29.62801077299617</v>
+        <v>29.6934185882096</v>
       </c>
       <c r="O2" t="n">
-        <v>5.443161836010039</v>
+        <v>5.449166779261724</v>
       </c>
       <c r="P2" t="n">
-        <v>326.8389543044394</v>
+        <v>326.9048887262711</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17878,28 +17940,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0794280017263839</v>
+        <v>-0.08282906304194097</v>
       </c>
       <c r="J3" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="K3" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02756435604592211</v>
+        <v>0.02996910025992627</v>
       </c>
       <c r="M3" t="n">
-        <v>2.631414591599939</v>
+        <v>2.635239610642481</v>
       </c>
       <c r="N3" t="n">
-        <v>11.08291472673469</v>
+        <v>11.1070830065101</v>
       </c>
       <c r="O3" t="n">
-        <v>3.329101189020046</v>
+        <v>3.332729062871763</v>
       </c>
       <c r="P3" t="n">
-        <v>333.4192679414205</v>
+        <v>333.4595160933752</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17956,28 +18018,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.09077081616439481</v>
+        <v>-0.0985745244108262</v>
       </c>
       <c r="J4" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="K4" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02772330224868846</v>
+        <v>0.03202241379861037</v>
       </c>
       <c r="M4" t="n">
-        <v>2.93663139603497</v>
+        <v>2.96338671290714</v>
       </c>
       <c r="N4" t="n">
-        <v>14.38901610469076</v>
+        <v>14.69140303039419</v>
       </c>
       <c r="O4" t="n">
-        <v>3.793285660834254</v>
+        <v>3.832936606623464</v>
       </c>
       <c r="P4" t="n">
-        <v>337.9073651631218</v>
+        <v>337.9997121665417</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18015,7 +18077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E501"/>
+  <dimension ref="A1:E503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31545,6 +31607,60 @@
         </is>
       </c>
     </row>
+    <row r="502">
+      <c r="A502" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>-45.37219631962278,170.8660197051991</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>-45.37259407487258,170.8652861767797</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>-45.37307208349826,170.86466526713372</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:00+00:00</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>-45.372198596252346,170.86602151456722</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>-45.372593230566984,170.86528522176647</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>-45.37307335232037,170.86466725384824</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0487/nzd0487.xlsx
+++ b/data/nzd0487/nzd0487.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E503"/>
+  <dimension ref="A1:E505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10995,6 +10995,48 @@
         <v>326</v>
       </c>
       <c r="E503" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="n">
+        <v>318.12</v>
+      </c>
+      <c r="C504" t="n">
+        <v>327.01</v>
+      </c>
+      <c r="D504" t="n">
+        <v>326.35</v>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:13+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>319.12</v>
+      </c>
+      <c r="C505" t="n">
+        <v>327.53</v>
+      </c>
+      <c r="D505" t="n">
+        <v>326.67</v>
+      </c>
+      <c r="E505" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11011,7 +11053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B668"/>
+  <dimension ref="A1:B670"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17694,6 +17736,26 @@
       </c>
       <c r="B668" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B669" t="n">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B670" t="n">
+        <v>0.43</v>
       </c>
     </row>
   </sheetData>
@@ -17862,28 +17924,28 @@
         <v>0.07530000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0725038898119062</v>
+        <v>-0.07764009689279056</v>
       </c>
       <c r="J2" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="K2" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="L2" t="n">
-        <v>0.008777207173976564</v>
+        <v>0.01008276237635453</v>
       </c>
       <c r="M2" t="n">
-        <v>4.465031315489406</v>
+        <v>4.475687156695315</v>
       </c>
       <c r="N2" t="n">
-        <v>29.6934185882096</v>
+        <v>29.7333994806502</v>
       </c>
       <c r="O2" t="n">
-        <v>5.449166779261724</v>
+        <v>5.452834077858064</v>
       </c>
       <c r="P2" t="n">
-        <v>326.9048887262711</v>
+        <v>326.9658495967445</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17940,28 +18002,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.08282906304194097</v>
+        <v>-0.08603702402325393</v>
       </c>
       <c r="J3" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="K3" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02996910025992627</v>
+        <v>0.03234925555130563</v>
       </c>
       <c r="M3" t="n">
-        <v>2.635239610642481</v>
+        <v>2.638237092032189</v>
       </c>
       <c r="N3" t="n">
-        <v>11.1070830065101</v>
+        <v>11.1244405126591</v>
       </c>
       <c r="O3" t="n">
-        <v>3.332729062871763</v>
+        <v>3.335332144278753</v>
       </c>
       <c r="P3" t="n">
-        <v>333.4595160933752</v>
+        <v>333.4975915868682</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18018,28 +18080,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0985745244108262</v>
+        <v>-0.1057435224802225</v>
       </c>
       <c r="J4" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="K4" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03202241379861037</v>
+        <v>0.03624257070389547</v>
       </c>
       <c r="M4" t="n">
-        <v>2.96338671290714</v>
+        <v>2.987157403894106</v>
       </c>
       <c r="N4" t="n">
-        <v>14.69140303039419</v>
+        <v>14.93858162862252</v>
       </c>
       <c r="O4" t="n">
-        <v>3.832936606623464</v>
+        <v>3.86504613538086</v>
       </c>
       <c r="P4" t="n">
-        <v>337.9997121665417</v>
+        <v>338.0848067512389</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18077,7 +18139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E503"/>
+  <dimension ref="A1:E505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31661,6 +31723,60 @@
         </is>
       </c>
     </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>-45.37219679064958,170.8660200795511</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>-45.372592949131786,170.86528490342874</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>-45.37307546702381,170.86467056503926</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:13+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>-45.372204641096246,170.86602631875226</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>-45.3725966077893,170.86528904181952</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>-45.37307740046686,170.8646735924141</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
